--- a/data/trans_bre/P1403-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1403-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,92</t>
+          <t>-3,23; 4,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 9,28</t>
+          <t>0,16; 9,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 8,66</t>
+          <t>0,17; 8,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 7,38</t>
+          <t>-0,45; 6,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 28,65</t>
+          <t>-18,65; 30,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 53,68</t>
+          <t>0,59; 54,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 65,31</t>
+          <t>1,58; 63,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 39,13</t>
+          <t>-2,3; 36,2</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 9,67</t>
+          <t>2,9; 9,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,55</t>
+          <t>0,88; 7,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 4,81</t>
+          <t>-1,87; 4,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 13,16</t>
+          <t>-1,46; 4,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,73; 92,14</t>
+          <t>20,55; 86,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 55,22</t>
+          <t>5,15; 55,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 34,27</t>
+          <t>-10,78; 32,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 169,2</t>
+          <t>-8,09; 26,46</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,06</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>-14,81%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,42</t>
+          <t>0,7; 8,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 6,39</t>
+          <t>-1,83; 6,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 7,53</t>
+          <t>-0,37; 7,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 47,29</t>
+          <t>-6,73; 0,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 77,48</t>
+          <t>4,52; 75,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 48,9</t>
+          <t>-11,12; 45,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 58,29</t>
+          <t>-2,57; 63,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 259,5</t>
+          <t>-30,86; 5,66</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,27</t>
+          <t>0,5; 6,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 8,64</t>
+          <t>1,16; 8,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 5,12</t>
+          <t>-1,17; 5,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 6,11</t>
+          <t>1,09; 7,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 67,47</t>
+          <t>2,44; 60,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 50,92</t>
+          <t>5,57; 49,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 36,57</t>
+          <t>-7,17; 40,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 33,49</t>
+          <t>5,17; 43,15</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,19</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,75</t>
+          <t>2,31; 5,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,92</t>
+          <t>2,13; 5,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,33</t>
+          <t>0,75; 4,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 22,99</t>
+          <t>0,08; 3,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,76; 48,07</t>
+          <t>16,24; 47,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,86; 36,81</t>
+          <t>11,78; 37,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 30,04</t>
+          <t>4,7; 30,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 139,52</t>
+          <t>0,36; 19,05</t>
         </is>
       </c>
     </row>
